--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_317_R32.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_317_R32.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.662</v>
+        <v>5.4176</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8594</v>
+        <v>6.4806</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1975</v>
+        <v>-1.0631</v>
       </c>
       <c r="G2" t="n">
         <v>4.647</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6808999999999999</v>
+        <v>0.0747</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.507</v>
+        <v>0.1142</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.174</v>
+        <v>-0.0395</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2384</v>
+        <v>1.9524</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5355</v>
+        <v>2.4175</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2971</v>
+        <v>-0.4652</v>
       </c>
       <c r="G3" t="n">
         <v>1.0413</v>
@@ -688,13 +688,13 @@
         <v>0.4639</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7332</v>
+        <v>0.4472</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5113</v>
+        <v>0.3934</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2219</v>
+        <v>0.0538</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3934</v>
+        <v>1.6221</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1153</v>
+        <v>0.6157</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5087</v>
+        <v>1.0064</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9146</v>
+        <v>1.5025</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09130000000000001</v>
+        <v>1.1009</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8233</v>
+        <v>0.4016</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6717</v>
+        <v>1.2132</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5244</v>
+        <v>1.1763</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1472</v>
+        <v>0.0368</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2429</v>
+        <v>0.2893</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4331</v>
+        <v>-0.0755</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6761</v>
+        <v>0.3648</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1025</v>
+        <v>-0.8984</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6201</v>
+        <v>-0.5975</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4824</v>
+        <v>-0.3009</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3458</v>
+        <v>0.7936</v>
       </c>
       <c r="E5" t="n">
-        <v>0.541</v>
+        <v>1.0811</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8047</v>
+        <v>-0.2875</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5025</v>
+        <v>3.8711</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1009</v>
+        <v>1.4018</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4016</v>
+        <v>2.4693</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2132</v>
+        <v>4.1535</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1763</v>
+        <v>1.6776</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0368</v>
+        <v>2.4759</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2893</v>
+        <v>-0.2824</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0755</v>
+        <v>-0.2759</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3648</v>
+        <v>-0.0065</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1598</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1747</v>
+        <v>-0.5957</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6721</v>
+        <v>-0.2711</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5026</v>
+        <v>-0.3246</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4096</v>
+        <v>0.1184</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1676</v>
+        <v>-1.1887</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.758</v>
+        <v>1.3071</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8711</v>
+        <v>0.9146</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4018</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4693</v>
+        <v>0.8233</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1535</v>
+        <v>0.6717</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6776</v>
+        <v>0.5244</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4759</v>
+        <v>0.1472</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2824</v>
+        <v>0.2429</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2759</v>
+        <v>-0.4331</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0065</v>
+        <v>0.6761</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0876</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9796</v>
+        <v>0.8274</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1845</v>
+        <v>0.5467</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7951</v>
+        <v>0.2807</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
         <v>-1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1064</v>
+        <v>-0.352</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.2471</v>
+        <v>-3.5263</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1407</v>
+        <v>3.1743</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1234</v>
@@ -1000,13 +1000,13 @@
         <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3211</v>
+        <v>0.0756</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2047</v>
+        <v>-0.0745</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1164</v>
+        <v>0.15</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1703</v>
+        <v>-0.5936</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.835</v>
+        <v>-3.2978</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3353</v>
+        <v>2.7041</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0278</v>
+        <v>3.0169</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1801</v>
+        <v>4.3921</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2079</v>
+        <v>-1.3752</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7527</v>
+        <v>2.1665</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0336</v>
+        <v>4.0605</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7863</v>
+        <v>-1.894</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2751</v>
+        <v>0.8504</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1465</v>
+        <v>0.3317</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4216</v>
+        <v>0.5188</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-5.7988</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2842</v>
+        <v>0.4048</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.224</v>
+        <v>0.3345</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0602</v>
+        <v>0.0703</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6433</v>
+        <v>-1.0187</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3475</v>
+        <v>-0.717</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7041</v>
+        <v>-0.3016</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0169</v>
+        <v>-1.0278</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3921</v>
+        <v>0.1801</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3752</v>
+        <v>-1.2079</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1665</v>
+        <v>-0.7527</v>
       </c>
       <c r="K9" t="n">
-        <v>4.0605</v>
+        <v>0.0336</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.894</v>
+        <v>-0.7863</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8504</v>
+        <v>-0.2751</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3317</v>
+        <v>0.1465</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5188</v>
+        <v>-0.4216</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.7988</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3195</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6449</v>
+        <v>-0.1327</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.1061</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0703</v>
+        <v>-0.0266</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2563</v>
+        <v>-1.9586</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8172</v>
+        <v>-2.3117</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4391</v>
+        <v>0.3531</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0698</v>
+        <v>-3.2264</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5596</v>
+        <v>-2.497</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6295</v>
+        <v>-0.7294</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.102</v>
+        <v>-3.3656</v>
       </c>
       <c r="K10" t="n">
-        <v>0.521</v>
+        <v>-2.2211</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.6229</v>
+        <v>-1.1445</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0322</v>
+        <v>0.1392</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0387</v>
+        <v>-0.2759</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0065</v>
+        <v>0.415</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4941</v>
+        <v>0.572</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4446</v>
+        <v>1.0539</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0495</v>
+        <v>-0.4819</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3364</v>
+        <v>-2.3244</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6223</v>
+        <v>-1.314</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2859</v>
+        <v>-1.0104</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.2264</v>
+        <v>-1.0698</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.497</v>
+        <v>0.5596</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7294</v>
+        <v>-1.6295</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.3656</v>
+        <v>-1.102</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2211</v>
+        <v>0.521</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1445</v>
+        <v>-1.6229</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1392</v>
+        <v>0.0322</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2759</v>
+        <v>0.0387</v>
       </c>
       <c r="O11" t="n">
-        <v>0.415</v>
+        <v>-0.0065</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1942</v>
+        <v>1.426</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7433</v>
+        <v>0.9478</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5491</v>
+        <v>0.4782</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5365</v>
+        <v>3.6568</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8809</v>
+        <v>-1.760600000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>5.4171</v>
+        <v>5.4172</v>
       </c>
       <c r="G12" t="n">
         <v>8.545999999999999</v>
@@ -1390,19 +1390,19 @@
         <v>11.5977</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0808</v>
+        <v>2.2009</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2212</v>
+        <v>2.3413</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1405000000000001</v>
+        <v>-0.1405</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6109</v>
       </c>
       <c r="W12" t="n">
-        <v>4.0363</v>
+        <v>4.036300000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-7.6472</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6223</v>
+        <v>3.2299</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8484</v>
+        <v>2.6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2261</v>
+        <v>0.6299</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1084</v>
+        <v>0.3565</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.163</v>
+        <v>0.755</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2715</v>
+        <v>-0.3984</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9776</v>
+        <v>1.812</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1211</v>
+        <v>2.679</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8564000000000001</v>
+        <v>-0.867</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8691</v>
+        <v>-1.4555</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2842</v>
+        <v>-1.924</v>
       </c>
       <c r="O13" t="n">
-        <v>0.415</v>
+        <v>0.4685</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2819</v>
+        <v>0.9456</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9584</v>
+        <v>0.2519</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6765</v>
+        <v>0.6937</v>
       </c>
       <c r="V13" t="n">
         <v>0.5361</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>J. NEBO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4943</v>
+        <v>1.8942</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2462</v>
+        <v>0.8377</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2481</v>
+        <v>1.0565</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3565</v>
+        <v>-2.4511</v>
       </c>
       <c r="H14" t="n">
-        <v>0.755</v>
+        <v>-2.8762</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3984</v>
+        <v>0.4251</v>
       </c>
       <c r="J14" t="n">
-        <v>1.812</v>
+        <v>-1.55</v>
       </c>
       <c r="K14" t="n">
-        <v>2.679</v>
+        <v>-1.7709</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.867</v>
+        <v>0.2208</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4555</v>
+        <v>-0.9011</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.924</v>
+        <v>-1.1053</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4685</v>
+        <v>0.2042</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>0.21</v>
+        <v>0.291</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1019</v>
+        <v>0.1891</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3119</v>
+        <v>0.1019</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5361</v>
+        <v>3.3584</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5361</v>
+        <v>3.3584</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. NEBO</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3824</v>
+        <v>1.8359</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6634</v>
+        <v>1.433</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7191</v>
+        <v>0.4029</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.4511</v>
+        <v>0.1084</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.8762</v>
+        <v>-1.163</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4251</v>
+        <v>1.2715</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.55</v>
+        <v>0.9776</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.7709</v>
+        <v>0.1211</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2208</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9011</v>
+        <v>-0.8691</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1053</v>
+        <v>-1.2842</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2042</v>
+        <v>0.415</v>
       </c>
       <c r="P15" t="n">
         <v>0.6959</v>
@@ -1624,28 +1624,28 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7793</v>
+        <v>0.4955</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0148</v>
+        <v>0.543</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2355</v>
+        <v>-0.0474</v>
       </c>
       <c r="V15" t="n">
-        <v>3.3584</v>
+        <v>0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3584</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>S. TONUT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5565</v>
+        <v>1.3312</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0953</v>
+        <v>-0.3426</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4612</v>
+        <v>1.6738</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3239</v>
+        <v>-0.1912</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4477</v>
+        <v>-0.0707</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1239</v>
+        <v>-0.1205</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1947</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1211</v>
+        <v>0.1512</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0736</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5185999999999999</v>
+        <v>0.4071</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5688</v>
+        <v>-0.222</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0502</v>
+        <v>0.6291</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8623</v>
+        <v>1.0585</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9006</v>
+        <v>0.2557</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0382</v>
+        <v>0.8028</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. TONUT</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9374</v>
+        <v>1.1512</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8144</v>
+        <v>0.3876</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7518</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1912</v>
+        <v>-0.3239</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0707</v>
+        <v>-0.4477</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1205</v>
+        <v>0.1239</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5983000000000001</v>
+        <v>0.1947</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1512</v>
+        <v>0.1211</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.0736</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4071</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.222</v>
+        <v>-0.5688</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6291</v>
+        <v>0.0502</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6647</v>
+        <v>0.4571</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2161</v>
+        <v>0.1928</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8808</v>
+        <v>0.2642</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>M. GUDURIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4182</v>
+        <v>0.2537</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0314</v>
+        <v>-1.3438</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3867</v>
+        <v>1.5976</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.4529</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0838</v>
+        <v>-0.4705</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4049</v>
+        <v>0.9234</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0913</v>
+        <v>1.1647</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1783</v>
+        <v>0.8136</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0871</v>
+        <v>0.3511</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4123</v>
+        <v>-0.7119</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0945</v>
+        <v>-1.2842</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3178</v>
+        <v>0.5723</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9278</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-4.639</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3668</v>
+        <v>-0.7921</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1968</v>
+        <v>-0.55</v>
       </c>
       <c r="U18" t="n">
-        <v>0.17</v>
+        <v>-0.242</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>2.6805</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GUDURIC</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3633</v>
+        <v>-0.1766</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2874</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9241</v>
+        <v>-0.2631</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4529</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4705</v>
+        <v>1.0838</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9234</v>
+        <v>-0.4049</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1647</v>
+        <v>2.0913</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8136</v>
+        <v>2.1783</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3511</v>
+        <v>-0.0871</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7119</v>
+        <v>-1.4123</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2842</v>
+        <v>-1.0945</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5723</v>
+        <v>-0.3178</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0876</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5515</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.4091</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4936</v>
+        <v>0.3148</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9155</v>
+        <v>0.2937</v>
       </c>
       <c r="V19" t="n">
-        <v>2.6805</v>
+        <v>-0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3729</v>
+        <v>-1.097</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3081</v>
+        <v>-0.9543</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0648</v>
+        <v>-0.1427</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2799</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0514</v>
+        <v>0.3273</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5149</v>
+        <v>-0.161</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5663</v>
+        <v>0.4883</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8748</v>
+        <v>-3.0155</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6463</v>
+        <v>-2.2925</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2285</v>
+        <v>-0.7231</v>
       </c>
       <c r="G21" t="n">
         <v>-2.07</v>
@@ -2092,13 +2092,13 @@
         <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5187</v>
+        <v>-0.6594</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7073</v>
+        <v>-0.3534</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8114</v>
+        <v>-0.306</v>
       </c>
       <c r="V21" t="n">
         <v>-1.214</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5</v>
+        <v>-4.798</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.1826</v>
+        <v>-5.8288</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6826</v>
+        <v>1.0307</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8266</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3693</v>
+        <v>-0.6673</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8962</v>
+        <v>-0.5423</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4731</v>
+        <v>-0.125</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5363</v>
+        <v>0.609</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4169</v>
+        <v>-5.4172</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8808</v>
+        <v>6.0261</v>
       </c>
       <c r="G23" t="n">
         <v>-8.545999999999999</v>
@@ -2224,7 +2224,7 @@
         <v>-1.6073</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1837000000000004</v>
+        <v>0.1837</v>
       </c>
       <c r="L23" t="n">
         <v>-1.7913</v>
@@ -2233,7 +2233,7 @@
         <v>-6.938600000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-9.265000000000002</v>
+        <v>-9.264999999999999</v>
       </c>
       <c r="O23" t="n">
         <v>2.3262</v>
@@ -2248,13 +2248,13 @@
         <v>15.0769</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0807</v>
+        <v>2.0646</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1405999999999995</v>
+        <v>0.1406000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2212</v>
+        <v>1.9242</v>
       </c>
       <c r="V23" t="n">
         <v>3.6109</v>
